--- a/metadata/plate_metadata/20260324_cep290_24hpf_plate01_well_metadata.xlsx
+++ b/metadata/plate_metadata/20260324_cep290_24hpf_plate01_well_metadata.xlsx
@@ -993,17 +993,17 @@
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="F2" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="H2" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="I2" s="6" t="inlineStr">
@@ -1050,17 +1050,17 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -1070,22 +1070,22 @@
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="J3" s="8" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="L3" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="K6" s="7" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -1343,17 +1343,17 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="J7" s="8" t="inlineStr">
@@ -1395,22 +1395,22 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr">
@@ -1457,17 +1457,17 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
